--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6782-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6782-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5993990-C498-4226-BB1F-CF8AF4D62AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF917758-831C-4F83-B09C-E37E09DFB685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5A841A26-78A4-40E0-9EFB-6F21D3284214}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{AB66936D-CA7F-4E54-84FD-0B5F4D059FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="6782-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1466,25 +1466,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26E03D36-BF28-45C7-AF59-B7850A96ADE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81DA0514-46C2-4729-A478-442971EC79C2}">
   <dimension ref="A1:X28"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1674,7 +1674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2023</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2022</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2021</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2020</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2019</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37" t="s">
         <v>43</v>
       </c>
